--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20211.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20211.xlsx
@@ -486,19 +486,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -512,19 +512,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>63.64</v>
+        <v>86.36</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -538,19 +538,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -603,16 +603,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="E2">
+        <v>5</v>
+      </c>
+      <c r="F2">
         <v>20</v>
       </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>80</v>
+      </c>
+      <c r="H2">
+        <v>6.7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -626,16 +629,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="E3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>72.73</v>
+      </c>
+      <c r="H3">
+        <v>6.4</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -649,16 +655,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="E4">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>84.62</v>
+      </c>
+      <c r="H4">
+        <v>6.5</v>
       </c>
     </row>
   </sheetData>
@@ -711,19 +720,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>88</v>
       </c>
       <c r="H2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -737,16 +746,16 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>63.64</v>
+        <v>86.36</v>
       </c>
       <c r="H3">
         <v>6.6</v>
@@ -763,19 +772,19 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>80.77</v>
+        <v>84.62</v>
       </c>
       <c r="H4">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +844,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Rodriguez Roman Marisol - Estadisticos 20211.xlsx
+++ b/docentes/Rodriguez Roman Marisol - Estadisticos 20211.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,15 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>VARGAS</t>
-  </si>
-  <si>
-    <t>KELLY ITZEL</t>
   </si>
 </sst>
 </file>
@@ -603,19 +594,19 @@
         <v>25</v>
       </c>
       <c r="D2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G2">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H2">
-        <v>6.7</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -629,19 +620,19 @@
         <v>22</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G3">
-        <v>72.73</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -655,7 +646,7 @@
         <v>26</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>4</v>
@@ -667,7 +658,7 @@
         <v>84.62</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -723,13 +714,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G2">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H2">
         <v>7</v>
@@ -749,16 +740,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G3">
-        <v>86.36</v>
+        <v>95.45</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -784,7 +775,7 @@
         <v>84.62</v>
       </c>
       <c r="H4">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
     </row>
   </sheetData>
@@ -794,7 +785,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -824,29 +815,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>17330051920191</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
